--- a/novels/shumatsu-no-sanctuary/案/終末のサンクチュアリ_制作シート.xlsx
+++ b/novels/shumatsu-no-sanctuary/案/終末のサンクチュアリ_制作シート.xlsx
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D38"/>
+  <dimension ref="B1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -932,29 +932,29 @@
     <row r="23">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>何の書類か(字コンテ)</t>
+          <t>字コンテとは</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>1話ぶんの「シナリオ設計シート」。「ネーム・作画担当さま」への指示が混ざるので、漫画(コミカライズ)の原作を、セリフとト書きの1行単位で書く書類。このファイルでは「字コンテ」と呼ぶ</t>
+          <t>ネーム・作画担当さま向けの、1話ぶんのシナリオ設計シート。セリフとト書きを1行ずつ書く。見出しは、サブタイトルと、話の目的/見せたいもの</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>推測(注記と見た目から)</t>
+          <t>推測</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>ヘッダ</t>
+          <t>列と構成</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>サブタイトル(緑の見出し)と、話の目的/見せたいもの(黄色の帯)。ページが変わっても、同じ見出しが上に出る</t>
+          <t>A文字数/B話者/Cシナリオ内容/Dキャラ情報/E心情・表情・演出プラン/F備考。導入・山場1・山場2・ヒキの4ブロックで、ブロックごとに小計(例:548+681+437+332=1998字、セリフ54)</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -966,29 +966,29 @@
     <row r="25">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>列</t>
+          <t>色</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>A文字数(行ごと)/B話者/Cシナリオ内容/Dキャラ情報(場所・時間・背景。場面が変わるときに書く)/E心情・表情・演出プラン/Fその他備考(補足、イメージ画像の貼り付け)</t>
+          <t>赤字=魅せゴマ・キメ台詞(各ブロックに1つ以上)/青字=一番の見せ場(1つ)/ピンク字=強調(用途の説明なし)</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>確認</t>
+          <t>赤・青は確認</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>構成</t>
+          <t>心情</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>導入(500字以内)→山場1(1000字以内)→山場2(1000字以内)→ヒキ(500字以内)の4ブロック。ブロックごとに色の帯と小計がある</t>
+          <t>目に見えないものは、セリフと演技で表す</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
@@ -1000,145 +1000,43 @@
     <row r="27">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>分量の実例</t>
+          <t>各話あらすじ</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>導入548字・山場1 681字・山場2 437字・ヒキ332字で、合計1998字。セリフは54個。目安の「以内」は厳密ではなく、導入は48字超えている</t>
+          <t>「やりたいこと」1〜2行+1〜4の番号つき4項目(4はヒキ)で約500字。前の話を指す書き方と、要の台詞の引用がある</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>確認(数字は見た目から転記)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>1行の書き方</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>1行に、セリフ1つか動作1つ。セリフは話者をB列に書き、C列は「」で始める。ト書きは「」なしで、話者列は空にする</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
           <t>確認</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>色のルール</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>赤字=魅せゴマ・キメ台詞(導入・山場・ヒキで、必ず1つ以上)/青字=この話で一番の見せ場(スーパーカット)を指定/ピンク字=演出プランなどに出るが、用途の説明はない(強調と推測)</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>赤・青は確認、ピンクは推測</t>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>提出前の自己点検</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>心情の書き方</t>
-        </is>
-      </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>心情描写など「目に見えないもの」は、セリフと演技で表す。モノローグでの説明は求めていない</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>確認</t>
+          <t>字コンテ: 合計が目安の範囲か/赤字が導入・山場・ヒキに1つ以上あるか/青字が1つか/ミナの台詞に数字がないか</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>集計</t>
-        </is>
-      </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>行ごとの文字数、ブロックの小計、話の合計、セリフ数が出ている。式は見えないので、同じ結果が出る式を作った(行の文字数=LEN、セリフ数=「で始まる行の数)</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>推測</t>
+          <t>全話共通: 確定事項と衝突していないか(CLAUDE.md)/設定にないことを足していないか/読者が予想する展開10個を出して避けたか</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>各話あらすじの書式(2つ目のPDF)</t>
-        </is>
-      </c>
       <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>各話、「やりたいこと」を1〜2行で書き、そのあとに1〜4の番号つきの4項目を書く。4つ目に「(ヒキ)」と書いてあるので、1〜3は導入・山場・山場に当たる。全体で約500字。前の話を指す書き方(「37話で……と言った」)と、要になる台詞の引用がある</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>確認(字数は見た目から概算)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>あらすじと字コンテの関係</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>あらすじを先に決めて、そのあと字コンテで台詞とト書きに展開する順番と読める</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>推測</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>提出前の自己点検</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>字コンテ: 合計が目安の範囲か/赤字が導入・山場・ヒキに1つ以上あるか/青字が1つか/ミナの台詞に数字がないか</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>全話共通: 確定事項と衝突していないか(CLAUDE.md)/設定にないことを足していないか/読者が予想する展開10個を出して避けたか</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>色: 赤=魅せゴマ・キメ台詞、青=一番の見せ場。E列の「★」で始まる行はピンクで出る(強調したい表情・演出)</t>
         </is>
@@ -3814,7 +3712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3844,11 +3742,11 @@
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="24">
-        <f>"文字数"&amp;CHAR(10)&amp;(A5+A14+A23+A32)</f>
+        <f>"文字数"&amp;CHAR(10)&amp;(A5+A9+A13+A17)</f>
         <v/>
       </c>
       <c r="B4" s="24">
-        <f>"セリフ数:"&amp;CHAR(10)&amp;COUNTIF(C6:C40,"「*")</f>
+        <f>"セリフ数:"&amp;CHAR(10)&amp;COUNTIF(C6:C20,"「*")</f>
         <v/>
       </c>
       <c r="C4" s="25" t="inlineStr">
@@ -3881,7 +3779,7 @@
     </row>
     <row r="5">
       <c r="A5" s="27">
-        <f>SUM(A6:A13)</f>
+        <f>SUM(A6:A8)</f>
         <v/>
       </c>
       <c r="B5" s="28" t="inlineStr">
@@ -3934,15 +3832,25 @@
       <c r="F8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="31">
-        <f>IF(C9="","",LEN(C9))</f>
-        <v/>
-      </c>
-      <c r="B9" s="32" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
+      <c r="A9" s="37">
+        <f>SUM(A10:A12)</f>
+        <v/>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>山場1</t>
+        </is>
+      </c>
+      <c r="C9" s="39">
+        <f>"※"&amp;使い方!$C$6&amp;"文字以内"</f>
+        <v/>
+      </c>
+      <c r="D9" s="40" t="n"/>
+      <c r="E9" s="39">
+        <f>"目安との差 "&amp;TEXT(A9-使い方!$C$6,"+0;-0;0")&amp;"字"</f>
+        <v/>
+      </c>
+      <c r="F9" s="40" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="31">
@@ -3978,36 +3886,36 @@
       <c r="F12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="31">
-        <f>IF(C13="","",LEN(C13))</f>
-        <v/>
-      </c>
-      <c r="B13" s="32" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
+      <c r="A13" s="42">
+        <f>SUM(A14:A16)</f>
+        <v/>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>山場2</t>
+        </is>
+      </c>
+      <c r="C13" s="44">
+        <f>"※"&amp;使い方!$C$7&amp;"文字以内"</f>
+        <v/>
+      </c>
+      <c r="D13" s="45" t="n"/>
+      <c r="E13" s="44">
+        <f>"目安との差 "&amp;TEXT(A13-使い方!$C$7,"+0;-0;0")&amp;"字"</f>
+        <v/>
+      </c>
+      <c r="F13" s="45" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="37">
-        <f>SUM(A15:A22)</f>
-        <v/>
-      </c>
-      <c r="B14" s="38" t="inlineStr">
-        <is>
-          <t>山場1</t>
-        </is>
-      </c>
-      <c r="C14" s="39">
-        <f>"※"&amp;使い方!$C$6&amp;"文字以内"</f>
-        <v/>
-      </c>
-      <c r="D14" s="40" t="n"/>
-      <c r="E14" s="39">
-        <f>"目安との差 "&amp;TEXT(A14-使い方!$C$6,"+0;-0;0")&amp;"字"</f>
-        <v/>
-      </c>
-      <c r="F14" s="40" t="n"/>
+      <c r="A14" s="31">
+        <f>IF(C14="","",LEN(C14))</f>
+        <v/>
+      </c>
+      <c r="B14" s="32" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="31">
@@ -4032,15 +3940,25 @@
       <c r="F16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="31">
-        <f>IF(C17="","",LEN(C17))</f>
-        <v/>
-      </c>
-      <c r="B17" s="32" t="n"/>
-      <c r="C17" s="33" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
+      <c r="A17" s="46">
+        <f>SUM(A18:A20)</f>
+        <v/>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>ヒキ</t>
+        </is>
+      </c>
+      <c r="C17" s="48">
+        <f>"※"&amp;使い方!$C$8&amp;"文字以内"</f>
+        <v/>
+      </c>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="48">
+        <f>"目安との差 "&amp;TEXT(A17-使い方!$C$8,"+0;-0;0")&amp;"字"</f>
+        <v/>
+      </c>
+      <c r="F17" s="49" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="31">
@@ -4075,254 +3993,14 @@
       <c r="E20" s="15" t="n"/>
       <c r="F20" s="15" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="31">
-        <f>IF(C21="","",LEN(C21))</f>
-        <v/>
-      </c>
-      <c r="B21" s="32" t="n"/>
-      <c r="C21" s="33" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
-    </row>
     <row r="22">
-      <c r="A22" s="31">
-        <f>IF(C22="","",LEN(C22))</f>
-        <v/>
-      </c>
-      <c r="B22" s="32" t="n"/>
-      <c r="C22" s="33" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="42">
-        <f>SUM(A24:A31)</f>
-        <v/>
-      </c>
-      <c r="B23" s="43" t="inlineStr">
-        <is>
-          <t>山場2</t>
-        </is>
-      </c>
-      <c r="C23" s="44">
-        <f>"※"&amp;使い方!$C$7&amp;"文字以内"</f>
-        <v/>
-      </c>
-      <c r="D23" s="45" t="n"/>
-      <c r="E23" s="44">
-        <f>"目安との差 "&amp;TEXT(A23-使い方!$C$7,"+0;-0;0")&amp;"字"</f>
-        <v/>
-      </c>
-      <c r="F23" s="45" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="31">
-        <f>IF(C24="","",LEN(C24))</f>
-        <v/>
-      </c>
-      <c r="B24" s="32" t="n"/>
-      <c r="C24" s="33" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="31">
-        <f>IF(C25="","",LEN(C25))</f>
-        <v/>
-      </c>
-      <c r="B25" s="32" t="n"/>
-      <c r="C25" s="33" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="15" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="31">
-        <f>IF(C26="","",LEN(C26))</f>
-        <v/>
-      </c>
-      <c r="B26" s="32" t="n"/>
-      <c r="C26" s="33" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="31">
-        <f>IF(C27="","",LEN(C27))</f>
-        <v/>
-      </c>
-      <c r="B27" s="32" t="n"/>
-      <c r="C27" s="33" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="31">
-        <f>IF(C28="","",LEN(C28))</f>
-        <v/>
-      </c>
-      <c r="B28" s="32" t="n"/>
-      <c r="C28" s="33" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="31">
-        <f>IF(C29="","",LEN(C29))</f>
-        <v/>
-      </c>
-      <c r="B29" s="32" t="n"/>
-      <c r="C29" s="33" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="31">
-        <f>IF(C30="","",LEN(C30))</f>
-        <v/>
-      </c>
-      <c r="B30" s="32" t="n"/>
-      <c r="C30" s="33" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="31">
-        <f>IF(C31="","",LEN(C31))</f>
-        <v/>
-      </c>
-      <c r="B31" s="32" t="n"/>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="15" t="n"/>
-      <c r="F31" s="15" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="46">
-        <f>SUM(A33:A40)</f>
-        <v/>
-      </c>
-      <c r="B32" s="47" t="inlineStr">
-        <is>
-          <t>ヒキ</t>
-        </is>
-      </c>
-      <c r="C32" s="48">
-        <f>"※"&amp;使い方!$C$8&amp;"文字以内"</f>
-        <v/>
-      </c>
-      <c r="D32" s="49" t="n"/>
-      <c r="E32" s="48">
-        <f>"目安との差 "&amp;TEXT(A32-使い方!$C$8,"+0;-0;0")&amp;"字"</f>
-        <v/>
-      </c>
-      <c r="F32" s="49" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="31">
-        <f>IF(C33="","",LEN(C33))</f>
-        <v/>
-      </c>
-      <c r="B33" s="32" t="n"/>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="15" t="n"/>
-      <c r="F33" s="15" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="31">
-        <f>IF(C34="","",LEN(C34))</f>
-        <v/>
-      </c>
-      <c r="B34" s="32" t="n"/>
-      <c r="C34" s="33" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="15" t="n"/>
-      <c r="F34" s="15" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="31">
-        <f>IF(C35="","",LEN(C35))</f>
-        <v/>
-      </c>
-      <c r="B35" s="32" t="n"/>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="n"/>
-      <c r="F35" s="15" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="31">
-        <f>IF(C36="","",LEN(C36))</f>
-        <v/>
-      </c>
-      <c r="B36" s="32" t="n"/>
-      <c r="C36" s="33" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="31">
-        <f>IF(C37="","",LEN(C37))</f>
-        <v/>
-      </c>
-      <c r="B37" s="32" t="n"/>
-      <c r="C37" s="33" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="15" t="n"/>
-      <c r="F37" s="15" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="31">
-        <f>IF(C38="","",LEN(C38))</f>
-        <v/>
-      </c>
-      <c r="B38" s="32" t="n"/>
-      <c r="C38" s="33" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="15" t="n"/>
-      <c r="F38" s="15" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="31">
-        <f>IF(C39="","",LEN(C39))</f>
-        <v/>
-      </c>
-      <c r="B39" s="32" t="n"/>
-      <c r="C39" s="33" t="n"/>
-      <c r="D39" s="15" t="n"/>
-      <c r="E39" s="15" t="n"/>
-      <c r="F39" s="15" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="31">
-        <f>IF(C40="","",LEN(C40))</f>
-        <v/>
-      </c>
-      <c r="B40" s="32" t="n"/>
-      <c r="C40" s="33" t="n"/>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C42" s="10">
-        <f>(A5+A14+A23+A32)&amp;"字(目安 "&amp;使い方!$C$9&amp;"〜"&amp;使い方!$C$10&amp;"字)"</f>
+      <c r="C22" s="10">
+        <f>(A5+A9+A13+A17)&amp;"字(目安 "&amp;使い方!$C$9&amp;"〜"&amp;使い方!$C$10&amp;"字)"</f>
         <v/>
       </c>
     </row>
